--- a/气象/表格文件/多站记录或比较/连续多日平均地温最低记录收集.xlsx
+++ b/气象/表格文件/多站记录或比较/连续多日平均地温最低记录收集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD96FA49-42CB-4AA6-9DD9-7C86842D1A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8FDD86-1141-4BC4-AF02-080025AAE9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{280E0553-F9D6-4715-8A94-818FD8B17F29}"/>
   </bookViews>
@@ -157,14 +157,6 @@
   </si>
   <si>
     <t>黑龙江呼玛附近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外兴安岭西北地温中心附近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2023.1_17-18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -238,6 +230,14 @@
   </si>
   <si>
     <t>2026.1_18-19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外兴安岭北坡西部高原</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023.1_19-20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,6 +486,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -498,20 +504,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,13 +837,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13"/>
+      <c r="A1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" s="7" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -864,16 +864,16 @@
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>-67.5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>33</v>
+        <v>41</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>14</v>
@@ -902,7 +902,7 @@
       <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="10" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -915,17 +915,17 @@
         <v>-58.1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="3">
         <v>-57.5</v>
       </c>
@@ -940,7 +940,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="3">
@@ -949,7 +949,7 @@
       <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="11" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -957,32 +957,32 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="3">
         <v>-57.3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="18" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="3">
         <v>-59.5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
@@ -1004,7 +1004,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="15"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="3">
         <v>-54.6</v>
       </c>
@@ -1028,7 +1028,7 @@
       <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -1045,7 +1045,7 @@
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -1062,7 +1062,7 @@
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="8" t="s">
